--- a/rag_benchmarking/results/benchmark_results.xlsx
+++ b/rag_benchmarking/results/benchmark_results.xlsx
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>0.3822</v>
+        <v>0.3833</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>0.254</v>
+        <v>0.2566</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>9</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>44</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>0.729</v>
+        <v>0.762</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>0.229</v>
@@ -935,10 +935,10 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>0.9785</v>
+        <v>0.9397</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>0.7882</v>
+        <v>0.7648</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>0.6573</v>
+        <v>0.727</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>0.2122</v>
+        <v>0.2097</v>
       </c>
       <c r="D17" s="9" t="n">
         <v>0.5899</v>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>4</v>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>10</v>
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1234,13 +1234,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1321,16 +1321,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.54126</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2342,21 +2342,26 @@
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
+          <t>The total capital expenditure (CAPEX) and operating expenditure (OPEX) for an AD + CHP system before and after integrating microalgal cultivation are as follows:  
+- **CAPEX**:  
+  - **Before integration**: 198,631 € [1].  
+  - **After integration**: 230,167 € [1].  
+- **OPEX**:  
+  - **Before integration**: 12,216 €/year [3].  
+  - **After integration**: 13,455 €/year [3].  
+These values reflect a 10% increase in both CAPEX and OPEX upon integration, as explicitly stated in the techno-economic analysis [1,3].</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
           <t>The total capital expenditure (CAPEX) and operating expenditure (OPEX) for an AD + CHP system before and after integrating a microalgal cultivation system are as follows:  
 - **CAPEX**:  
-  - **Before integration**: 198,631 € [1][2].  
-  - **After integration**: 230,167 € [1][2].  
+  - **Standalone AD + CHP system**: 198,631 € [1].  
+  - **Integrated AD + CHP + microalgal cultivation system**: 230,167 € (a 10% increase) [1].  
 - **OPEX**:  
-  - **Before integration**: 12,216 €/year [4].  
-  - **After integration**: 13,455 €/year [3][4].  
-These values reflect a 10% increase in both CAPEX and OPEX upon integration, as explicitly stated in the contexts.</t>
-        </is>
-      </c>
-      <c r="E2" s="12" t="inlineStr">
-        <is>
-          <t>The total Capital Expenditure (CAPEX) for the standalone AD + CHP system was **198,631 €**, and it increased to **230,167 €** after integrating a microalgal cultivation system (a 10% increase) [1].  
-The total Operating Expenditure (OPEX) for the standalone AD + CHP system was **12,216 €/year**, rising to **13,455 €/year** (a 10% increase) after adding the microalgal cultivation system [2].  
-These values reflect the economic trade-offs associated with integrating microalgal systems for nutrient recycling and biomass valorisation.</t>
+  - **Standalone AD + CHP system**: 12,216 €/year [2].  
+  - **Integrated AD + CHP + microalgal cultivation system**: 13,455 €/year (a 10% increase) [2].  
+These values reflect the incremental financial burden of adding microalgal cultivation to the system.</t>
         </is>
       </c>
       <c r="F2" s="12" t="inlineStr">
@@ -2498,15 +2503,15 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>The highest CH₄ concentration (% v/v) reported in the summary table of photosynthetic biogas upgrading reactor configurations is **&gt;97%** (Table 4, context [4]). However, the table does not explicitly provide corresponding CO₂ or N₂ concentrations for this technology. The table only specifies the typical final CH₄ concentration range for photoautotrophic (photosynthesis) upgrading as **&gt;90–97% vol** and lists advantages/disadvantages but does not include post-upgrading gas composition data for CO₂ or N₂. 
-For context, other biogas upgrading techniques in the same table (e.g., ex-situ chemoautotrophic) achieve **&gt;90–95% CH₄**, but again, CO₂ and N₂ values are not detailed in this summary.</t>
+          <t>The highest CH₄ concentration (% v/v) reported in the summary table of photosynthetic biogas upgrading reactor configurations is **&gt;90–97%** for the **photoautotrophic (photosynthesis)** method [4]. However, the corresponding CO₂ and N₂ concentrations are not explicitly provided in the table or the described contexts. The table only specifies the final CH₄ concentration range for this technology and does not include detailed data on CO₂ or N₂ levels post-upgrading. 
+For context, initial biogas from anaerobic digestion (AD) typically contains **~70% CH₄**, **~10–20% CO₂**, and **~10–20% N₂** [2], but these values are not directly applicable to the upgraded biomethane produced via photosynthetic methods.</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>The highest CH₄ concentration reported in the contexts is **98.9%** (v/v) during stage I of the biogas upgrading process [10]. The corresponding CO₂ concentration in the upgraded biomethane during this stage was **0.3%** [10]. However, **N₂ concentrations are not explicitly mentioned** in the contexts for this specific stage. 
-In contrast, at higher L/G ratios (e.g., 5), CH₄ concentrations decreased to **94%**, with **N₂ reaching up to 12.8%** [8]. However, this corresponds to lower CH₄ values compared to the 98.9% reported in stage I. 
-Thus, the highest CH₄ concentration is **98.9%** with **CO₂ at 0.3%**, but **N₂ data is not provided** for this condition in the given contexts.</t>
+          <t>The highest CH₄ concentration reported in the contexts is **98.9 ± 0.2%** (v/v) in stage I of the biogas upgrading process [8]. At this stage, the corresponding CO₂ concentration in the upgraded biomethane was **0.3 ± 0.1%** (v/v) [8]. However, **N₂ concentrations are not explicitly reported** in the contexts for this specific condition. 
+In other contexts, N₂ content is mentioned in winter biomethane (6.51 ± 3.00%) [2], but this corresponds to lower CH₄ concentrations (88.19 ± 5.56%) and is not associated with the highest CH₄ value. 
+**Contexts cited:** [8].</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -2590,16 +2595,26 @@
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>The provided contexts do not contain specific numerical values or direct comparisons of CAPEX, OPEX, amortization period, or land requirements between HRAP-AC photosynthetic biogas upgrading and pressure swing adsorption (PSA). While general statements are made about the relative costs of physical/chemical technologies (e.g., PSA) versus photosynthetic systems (e.g., HRAP-AC), such as lower CAPEX for PSA but higher OPEX for photosynthetic systems [1][7], no quantitative data or conditions are explicitly reported for either technology in this regard. Therefore, the question cannot be answered with the information provided.</t>
+          <t>The economic performance of HRAP-AC photosynthetic biogas upgrading compared to pressure swing adsorption (PSA) is discussed in the literature as follows:  
+1. **CAPEX (Capital Expenditure):**  
+   - Physical/chemical technologies (including PSA) exhibit **lower CAPEX** than photosynthetic biogas upgrading systems like HRAP-AC. For instance, photosynthetic systems have a reported CAPEX of **$6034 μNm⁻³h⁻¹** (context 5), though specific values for PSA are not provided in the contexts.  
+2. **OPEX (Operational Expenditure):**  
+   - Photosynthetic biogas upgrading (HRAP-AC) has **lower OPEX** compared to physical/chemical methods like PSA. For example, the energy consumption for photosynthetic upgrading was **0.191 kWh/m³** of biogas treated (context 4), while PSA systems (as physical/chemical technologies) are noted to have **higher OPEX** (context 5).  
+3. **Amortization Period:**  
+   - **No specific data** on amortization periods for HRAP-AC or PSA are provided in the contexts.  
+4. **Land Requirements:**  
+   - **HRAP-AC systems** require significant land area, as illustrated by a pilot-scale HRAP with dimensions **180 L (82 cm width × 170 cm length × 15 cm depth)** (context 9). In contrast, **PSA systems** (context 2) are typically compact, though specific land use metrics are not quantified in the contexts.  
+In summary, HRAP-AC has **higher CAPEX but lower OPEX** than PSA, but **land requirements** for HRAP-AC are not directly comparable due to the absence of PSA-specific data in the contexts. Amortization periods are not addressed in the provided literature.</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>The provided contexts do not contain specific numerical data or direct comparisons between HRAP-AC photosynthetic biogas upgrading and pressure swing adsorption (PSA) in terms of **CAPEX, OPEX, amortization period, or land requirements**. While general statements are made about the relative costs and environmental impacts of physical/chemical technologies (e.g., PSA) versus photosynthetic methods (e.g., HRAP-AC), such as lower CAPEX for physical/chemical technologies but higher OPEX and environmental impacts for them compared to photosynthetic systems [1, 6], **no explicit metrics for PSA or HRAP-AC are reported** in the contexts. 
-For example:
-- Context [1] and [6] note that physical/chemical technologies (like PSA) have lower CAPEX but higher OPEX than photosynthetic upgrading, but **no CAPEX/OPEX values are quantified** for either technology.
-- Context [5] discusses energy consumption for photosynthetic upgrading (0.191 kWh/m³) but **does not compare this to PSA** or provide amortization or land-use data.
-Thus, **the question cannot be answered with the provided contexts**, as they lack the required specific economic and technical metrics for PSA or HRAP-AC.</t>
+          <t>The provided contexts do not explicitly compare the economic performance of HRAP-AC photosynthetic biogas upgrading with pressure swing adsorption (PSA) in terms of **CAPEX, OPEX, amortization period, or land requirements**. However, general insights about photosynthetic biogas upgrading versus physical/chemical technologies (which include PSA) are mentioned:  
+- **CAPEX**: Physical/chemical technologies (e.g., PSA) are noted to have **lower CAPEX** than photosynthetic biogas upgrading systems (e.g., HRAP-AC) [4].  
+- **OPEX**: Photosynthetic biogas upgrading is described as having **higher OPEX** compared to physical/chemical methods, though specific values for PSA are not provided [4].  
+- **Land requirements**: HRAP-AC systems require significant land area (e.g., a **1000 m² HRAP** for a specific biomass production rate [9]), but no land use data for PSA is mentioned in the contexts.  
+**Amortization period** is not discussed in any of the provided contexts.  
+In summary, while the contexts highlight general trends (lower CAPEX for PSA but higher OPEX for HRAP-AC), **specific numerical comparisons** between HRAP-AC and PSA for the requested metrics are **not available** in the provided materials.</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
@@ -2744,14 +2759,12 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>The energy demand for photosynthetic biogas upgrading is **0.191 kWh/m³** of biogas treated, compared to **0.200 kWh/m³** for membrane-based upgrading, as reported in the study's Figure 6 [1][2][3]. This indicates that photosynthetic upgrading consumes **9.5% less energy** per unit volume of biogas than membrane technology under the conditions described. The lower energy consumption of photosynthetic systems is attributed to their reliance on biological CO₂ absorption without requiring thermal input or high-pressure operations, unlike membrane technologies which depend on mechanical separation processes [3]. 
-Additionally, Table 4 from the same study confirms the energy consumption metric of **0.191 kWh/m³** for photosynthetic upgrading [10]. For membrane-based systems, the electricity demand range in Table 1 of another study is **0.2–0.35 kWh/m³**, with the specific value of **0.200 kWh/m³** cited in the context [4][6]. 
-These findings highlight the energy efficiency advantage of photosynthetic upgrading over membrane-based methods, particularly for small-scale applications.</t>
+          <t>The energy demand for photosynthetic biogas upgrading is **0.191 kWh/m³** of biogas treated, compared to **0.200 kWh/m³** for membrane-based upgrading [1][3]. This indicates that photosynthetic upgrading consumes **9.5% less energy** per cubic meter of biogas than membrane technology under the conditions described. These values are explicitly reported in the context, with the photosynthetic system highlighted as more energy-efficient for low-capacity applications [1][3].</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>The energy demand of photosynthetic biogas upgrading is lower than that of membrane-based upgrading. Specifically, photosynthetic upgrading consumes **0.191 kWh/m³** of biogas, whereas membrane technology requires **0.200 kWh/m³** [1][3]. This difference highlights the energy efficiency advantage of photosynthetic systems, which do not require thermal input for operation, unlike some conventional technologies [3].</t>
+          <t>The energy demand for photosynthetic biogas upgrading is **0.191 kWh/m³**, which is **lower than membrane-based upgrading** at **0.200 kWh/m³** [1][3][5]. This indicates that photosynthetic systems achieve greater energy efficiency compared to membrane technologies under the conditions described in the study. The lower energy consumption of photosynthetic upgrading is attributed to its reliance on sunlight as the primary energy source for CO₂ fixation, eliminating the need for external thermal inputs [3].</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -2860,28 +2873,37 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>For AD + CHP systems, the reported profitability indexes are as follows:  
-- **AD + CHP (Base case):**  
-  - **NPV:** 290,473 € [1]  
-  - **DPBT:** 6.4 years [1]  
-  - **IRR:** 19% [1]  
-  - **PI:** 1.4 [1]  
-- **AD + CHP + microalgae biofertilizers (Base case):**  
-  - **NPV:** 266,032 € [1]  
-  - **DPBT:** 7.1 years [1]  
-  - **IRR:** 16% [1]  
-  - **PI:** 1.16 [1]  
-- **AD + CHP + microalgae biostimulants (Base case):**  
-  - **NPV:** 829,790 € [1]  
-  - **DPBT:** 3.3 years [1]  
-  - **IRR:** 45% [1]  
-  - **PI:** 3.6 [1]  
-These values correspond to the base-case scenarios presented in the profitability analysis [1].</t>
+          <t>For AD + CHP systems, the reported financial metrics are as follows:  
+### **1. AD + CHP Base Case**  
+- **NPV**: 290,473 € [1]  
+- **Discounted Payback Time (DPBT)**: 6.4 years [1]  
+- **Internal Rate of Return (IRR)**: 19% [1]  
+- **Profitability Index (PI)**: 1.4 [1]  
+---
+### **2. AD + CHP + Microalgae Biofertilizers (Base Case)**  
+- **NPV**: 266,032 € [1]  
+- **DPBT**: 7.1 years [1]  
+- **IRR**: 16% [1]  
+- **PI**: 1.16 [1]  
+**Note**: Higher productivity scenarios (e.g., 9x productivity) show improved metrics:  
+- **NPV**: 285,028 € [1]  
+- **DPBT**: 6.8 years [1]  
+- **IRR**: 17% [1]  
+- **PI**: 1.24 [1]  
+---
+### **3. AD + CHP + Microalgae Biostimulants (Base Case)**  
+- **NPV**: 829,790 € [1]  
+- **DPBT**: 3.3 years [1]  
+- **IRR**: 45% [1]  
+- **PI**: 3.6 [1]  
+These values highlight the significant economic advantage of integrating microalgae for biostimulant production compared to biofertilizers or standalone AD + CHP systems [1].</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>The provided contexts do not explicitly report the Net Present Value (NPV), discounted payback time (DPBT), Internal Rate of Return (IRR), or profitability index (PI) for the base case (AD + CHP alone), microalgae biofertilizer scenarios, or microalgae biostimulants scenarios. While Context [4] mentions a DPBT of **3.3 years** and a PI of **3.6** for the biostimulants scenario, no numerical values for NPV, IRR, or other metrics are provided for any of the scenarios. The contexts focus on CAPEX, OPEX, revenue streams, and qualitative economic feasibility rather than detailed financial indices like NPV or IRR. Therefore, the specific requested data is not available in the provided sources.</t>
+          <t>The provided contexts do not explicitly report the **NPV (Net Present Value)**, **discounted payback time (DPBT)**, **IRR (Internal Rate of Return)**, or **profitability index (PI)** for the **base case (AD + CHP alone)**, **microalgae biofertilizer scenarios**, or **microalgae biostimulants scenarios**. 
+However, **context [4]** mentions that for the **biostimulants scenario**, the **DPBT is 3.3 years** and the **PI is 3.6**. No specific values for the base case or biofertilizer scenarios are provided in the contexts. The other contexts focus on **CAPEX**, **OPEX**, **revenues**, and **techno-economic trade-offs** but do not include the requested financial metrics (NPV, IRR) or additional details for the other scenarios. 
+Thus, the required data is **not fully available** in the provided contexts.</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -3024,15 +3046,18 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>The total plant cost (TPC) and total operational cost across the three scenarios in the algae-biogas-energy system are not explicitly provided in the given contexts. However, the largest contributor to operating costs in a related system (from context [3]) was **harvesting labor**, accounting for **NZD 1362/year** (64.6% of total operating costs of NZD 2109/year). 
-For the algae-biogas-energy system in context [1], the table only details **capital cost components** (e.g., site preparation, mixing, flue gas supply) with percentages of TPC but does not report the total TPC or operational costs. Thus, the specific numerical values for total plant and operational costs across the three scenarios are **not available** in the provided contexts.</t>
+          <t>The total plant cost (TPC) and total operational cost across the three scenarios in the algae-biogas-energy system are not explicitly provided in the given contexts. However, context [3] reports total operating costs for a specific system as **2109 NZD/year**, with **harvesting labor** being the largest contributor at **1362 NZD/year** (64.6% of total operating costs). 
+For the three scenarios in context [1], individual capital cost components (e.g., site preparation, mixing, etc.) are listed with their percentages of TPC, but no aggregated total plant cost or total operational cost is explicitly stated. Therefore, the requested numerical values for total plant and operational costs across the three scenarios are not available in the provided contexts.</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>The total installed cost for the algae-biogas-energy system across the three scenarios (direct recycle, CHG, AD) is reported as **$64 million** [10]. However, the context does not explicitly break down the **total plant costs** or **total operational costs** for each individual scenario. 
-Regarding the largest contributor to operating costs, the provided contexts do not specify this detail for the three scenarios in question. Context [10] highlights differences in **capital costs** (e.g., CHG has 64% higher capital costs than direct recycle) but does not address operational cost components. Other contexts (e.g., [4]) mention labor and depreciation as major costs in general scenarios but do not link them to the specific three scenarios described in [10]. 
-**Conclusion**: The total installed cost is **$64 million** [10], but scenario-specific plant and operational costs, as well as the largest contributor to operating costs, are not explicitly detailed in the provided contexts.</t>
+          <t>The total installed cost for the algae-biogas-energy system across the three scenarios (direct recycle, CHG, AD) was **$64 million** [10]. However, the provided contexts do not explicitly report the **total operational costs** for these scenarios. 
+Regarding the largest contributor to operating costs, **context [4]** indicates that **labor and depreciation** are the major costs in similar systems, while **electricity consumption for dewatering and drying** of algal biomass is a significant operational expense. However, this information is specific to a different study (abattoir-based microalgae production) and not directly tied to the three scenarios in context [10]. 
+In summary:  
+- **Total plant cost**: $64 million (for the three scenarios combined) [10].  
+- **Total operational cost**: Not explicitly reported in the provided contexts.  
+- **Largest contributor to operating costs**: Not specified for the three scenarios, but labor, depreciation, and electricity for dewatering/drying are highlighted in related studies [4].</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -3127,13 +3152,13 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>The context does not explicitly provide the total installed cost of the PBR support structure for microalgae cultivation in 2024 dollars. While context [2] and [5] mention the **PBR support structure cost** as **$20 per PBR bag**, the total number of bags or modules is not directly stated. However, using the provided parameters (e.g., 1000-acre cultivation area, 5 acres per module, 18,000 bags per module), one could infer the total number of bags (3.6 million) and calculate a total cost of **$72 million**. However, this calculation is not explicitly confirmed in the context, and the question specifically asks for the **total installed cost**, which is not directly reported. 
-Thus, the context does not contain the answer.</t>
+          <t>The total installed cost of the PBR support structure for microalgae cultivation is not explicitly provided in the contexts. However, the **PBR support structure cost** is mentioned as **$20 per PBR bag** in context [2] and [10]. Without additional data on the number of PBR bags or the total cultivation area, the total installed cost cannot be calculated from the provided information.</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>The provided contexts do not specify the total installed cost of the PBR (photobioreactor) support structure for microalgae cultivation in 2024 dollars. While some contexts discuss capital and operational costs for microalgae cultivation systems (e.g., HRAPs, MTPBRs, and PBRs), no explicit numerical value for the installed cost of a PBR support structure is reported. For example, context [4] mentions costs for HRAPs (high-rate algal ponds) but not PBRs, and context [8] references biomass production costs and sensitivity analysis parameters without providing installed cost figures for PBRs. Therefore, the answer cannot be determined from the given contexts.</t>
+          <t>The provided contexts do not specify the total installed cost of the PBR (photobioreactor) support structure for microalgae cultivation in 2024 dollars. While some contexts mention capital costs for PBR components (e.g., recirculation pumps, degassing columns, and chillers) [3], no explicit numerical value for the total installed cost of the PBR support structure is reported. Additionally, the contexts focus on operational costs, energy consumption, and economic feasibility analyses rather than providing a direct figure for installation costs. 
+Therefore, the answer cannot be determined from the given contexts.</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -3233,15 +3258,17 @@
       <c r="D9" s="12" t="inlineStr">
         <is>
           <t>The net electricity balance after accounting for electricity generated from methane for the three reactor types is as follows:  
-- **Horizontal tubular reactor**: **-82.3 GW h y⁻¹** (electricity generated from methane exceeded consumption, resulting in a surplus).  
-- **External loop reactor**: **-66.1 GW h y⁻¹** (similar surplus, though smaller than the horizontal tubular reactor).  
-- **Raceway pond**: **+62.0 GW h y⁻¹** (electricity consumption exceeded generation, resulting in a deficit).  
-These values are derived from Table 4 in context [4], which compares energy consumption and offsetting electricity production from methane in biodiesel production systems. The negative values indicate surplus electricity (generation &gt; consumption), while the positive value for the raceway pond indicates a deficit (consumption &gt; generation).</t>
+- **Horizontal tubular reactor**: **-82.3 GW h y⁻¹** (electricity consumption: 153.0 GW h y⁻¹; electricity production from methane: 70.7 GW h y⁻¹; net balance = consumption - production) [4].  
+- **External loop reactor**: **-66.1 GW h y⁻¹** (electricity consumption: 136.8 GW h y⁻¹; electricity production from methane: 70.7 GW h y⁻¹; net balance = consumption - production) [4].  
+- **Raceway pond**: **+62.0 GW h y⁻¹** (electricity consumption: 8.7 GW h y⁻¹; electricity production from methane: 70.7 GW h y⁻¹; net balance = consumption - production) [4].  
+These values reflect the surplus or deficit of electricity after offsetting consumption with methane-generated electricity. Negative values indicate a surplus (methane production exceeds consumption), while positive values indicate a deficit (consumption exceeds methane production).</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>The provided contexts do not contain specific numerical values or detailed information regarding the net electricity balance for horizontal tubular reactors, external loop reactors, or raceway ponds after accounting for electricity generated from methane. While some contexts discuss energy input/output calculations for anaerobic digestion systems (e.g., UASB reactors, HRAP systems) and mention equations for energy balance and net energy ratio (NER) [4, 10], no explicit data on net electricity balances for the reactor types specified in the question are reported. Therefore, the answer cannot be determined from the given contexts.</t>
+          <t>The provided contexts do not contain specific information about the net electricity balance for horizontal tubular reactors, external loop reactors, or raceway ponds after accounting for electricity generated from methane. The available data focuses on energy input/output calculations for UASB reactors and HRAP (horizontal raceway ponds) but does not address the specific reactors or metrics mentioned in the question. 
+For example, context [4] discusses energy inputs for UASB and HRAP systems, including pumping energy and methane yield calculations, but does not report net electricity balances. Similarly, context [10] describes energy balance equations (e.g., net energy ratio) but applies them to UASB reactors rather than the specified reactor types. No numerical values or conditions related to the question are explicitly stated in the contexts. 
+Therefore, the answer cannot be determined from the provided information.</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -3349,17 +3376,14 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>The total CO₂ equivalent reduction and annual carbon credit for the wastewater-based algal biofuel production system are as follows:  
-- **Total CO₂ equivalent reduction**: The calculation in the table indicates a net CO₂ equivalent value of **4,688,293 kg CO₂ eq./yr**, derived from the formula:  
-  $$(6) + (7) - (5) = 3,423,706\ \text{kg CO₂ eq./yr (emissions from wastewater treatment replaced)} + 2,409,074\ \text{kg CO₂ eq./yr (emissions from petroleum diesel replaced)} - 1,144,487\ \text{kg CO₂ eq./yr (emissions from electricity generation)}$$  
-  This value represents the **net emissions** after accounting for avoided emissions and new emissions from the system [1][2].  
-- **Annual carbon credit**: The carbon credit is explicitly stated as **$46,883/year** in the context, calculated based on the same emissions components (emissions from petroleum diesel replaced + emissions from wastewater treatment replaced – emissions from electricity generation) [5].  
-Note: The contexts do not explicitly clarify whether the **4,688,293 kg CO₂ eq./yr** value represents a net reduction or a net emission. The term "carbon credit" in the contexts refers to a **monetary value** ($46,883/year) rather than a CO₂ equivalent reduction.</t>
+          <t>The total CO₂ equivalent reduction estimated for the wastewater-based algal biofuel production system is **4,688,293 kg CO₂ eq./yr**, calculated as the sum of emissions from wastewater treatment replaced (3,423,706 kg CO₂ eq./yr) and petroleum diesel replaced (2,409,074 kg CO₂ eq./yr), minus emissions from electricity generation in the system (1,144,487 kg CO₂ eq./yr) [1][2]. 
+The annual carbon credit, represented as the monetary value of this reduction, was estimated at **$46,883/yr**, based on the same emissions calculations [5]. 
+These values reflect the net environmental benefit of the system, combining avoided emissions from wastewater treatment and diesel replacement, adjusted for electricity-related emissions.</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>The provided contexts do not explicitly report numerical values for total CO₂ equivalent reduction or annual carbon credit specific to wastewater-based algal biofuel production systems. While equations (e.g., Equation 3 in [3] and [6]) describe methodologies for calculating net GHG emissions and credits, no specific quantitative results (e.g., tonnage of CO₂ mitigated annually or monetary credit values) are given in the cited texts. Studies referenced (e.g., Mu et al., 2014 [2]; Gowd et al., 2025 [7]) emphasize environmental benefits but do not provide the requested numerical data within the context excerpts.</t>
+          <t>The provided contexts do not explicitly report specific numerical values for total CO₂ equivalent reduction or annual carbon credit for wastewater-based algal biofuel production systems. While equations and frameworks for calculating net emissions (e.g., Equation 3 in [3] and [6]) are described, no quantitative results (e.g., tonnage of CO₂ mitigated annually or monetary credit values) are given in the contexts. Studies referenced (e.g., Mu et al., 2014 [2]) focus on life cycle environmental impacts but do not provide the requested numerical data. Therefore, the answer cannot be determined from the provided contexts.</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
@@ -3438,24 +3462,25 @@
         <is>
           <t>The main annual cost savings and revenue sources for the wastewater-based algal biofuel production system are as follows:  
 ### **Cost Savings**  
-1. **Nutrient recycling**: \$550,000/yr from wastewater providing all nutrients (avoiding external nutrient purchases) [2].  
-2. **Centrate treatment avoidance**: \$564,768/yr from eliminating costs associated with centrate wastewater treatment [2, 9].  
-   - This includes \$164,768/yr in operational cost savings and \$400,000/yr in cover cost savings (e.g., reduced energy or chemical use) [9].  
-### **Revenue Streams**  
-1. **Bio-oil income**: Estimated as \$6,908X/yr, where *X* is the bio-oil price per barrel (dependent on market conditions). Calculated using a daily biomass yield of 10.298 tons, 28.6% conversion ratio, and 7.33 barrels/ton [9].  
-2. **Phosphorus (P) fertilizer sales**: \$232,455/yr from P-rich ash as a fertilizer, based on phosphate rock conversion and market pricing [9].  
-3. **Syngas income**: \$47,607/yr from syngas production, calculated using a 26% conversion ratio and lower heating value (LHV) ratio of 28.79% [9].  
-4. **Carbon credits**: \$46,883/yr from CO₂ emission reductions, derived from replacing petroleum diesel and wastewater treatment emissions [7, 8].  
-These figures highlight the economic viability of integrating nutrient recovery, coproduct valorisation, and carbon credits into wastewater-based algal biofuel systems [2, 9].</t>
+1. **Nutrient recycling**: \$550,000/yr from wastewater providing all nutrients (reducing external nutrient purchase costs) [2].  
+2. **Centrate treatment avoidance**: \$564,768/yr by eliminating the need for centrate treatment [2, 9].  
+3. **Wastewater treatment operation cost saving**: \$164,768/yr (calculated as 5420 ton/day * \$0.095/ton * 320 days/year) [9].  
+4. **Wastewater treatment cover cost saving**: \$400,000/yr (20% of a \$40,000,000 capital investment over 20 years) [9].  
+### **Revenue Sources**  
+1. **Bio-oil income**: \$6,908X/yr (dependent on bio-oil price *X*; calculated as 10.298 tons/day * 28.6% conversion ratio * \$X/bbl * 7.33 bbl/ton * 320 days/year) [9].  
+2. **Phosphorus (P) fertilizer sales**: \$232,455/yr (from P-rich ash as a coproduct; based on phosphate rock conversion and market value) [9].  
+3. **Syngas income**: \$47,607/yr (from syngas production; calculated using 26% conversion ratio and lower heating value (LHV) ratio) [9].  
+4. **Carbon credit**: \$46,883/yr (from CO₂ emission reductions compared to petroleum diesel and wastewater treatment scenarios) [7, 8].  
+These figures highlight the economic viability of integrating algal biofuel production with wastewater treatment, emphasizing cost reductions from nutrient and centrate management and revenue from biomass valorisation and carbon credits.</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>The provided contexts do not explicitly report specific annual cost savings or revenue sources for wastewater-based algal biofuel production systems. However, they mention factors that could influence financial performance, such as:  
-- **Feed-in tariffs** rewarding electrical and thermal energy production (context [3]).  
-- **Bio-oil yield improvements** potentially increasing internal rate of return (IRR) by reducing production costs (context [8]).  
-- **Crude oil price** and **bio-oil production cost thresholds** (e.g., bio-oil cost &lt; \$0.55/L for viability with \$80/barrel crude oil) (context [2]).  
-No specific numerical values for annual cost savings or revenues are quantified in the contexts.</t>
+          <t>The provided contexts do not explicitly report specific annual cost savings or revenue sources for wastewater-based algal biofuel production systems. However, the following relevant points are mentioned:  
+1. **Revenue from biomethane sales**: In a New Zealand case study, the maximum revenue from selling biomethane was estimated at **NZD 187/year** (context [4]). However, this was insufficient to offset operational costs, leading to annual deficits of **NZD 2101** (worst case) and **NZD 1922** (best case).  
+2. **Feed-in tariffs**: Context [3] notes that revenues from thermal and electrical energy production are rewarded equally via feed-in tariffs, though specific annual values are not quantified.  
+3. **Cost drivers**: Context [9] highlights that feedstock costs (assumed at **50 euros/t** for brown algae), maintenance, and operating costs (including biomass drying/pre-treatment) are major cost factors. Co-digestion with other wastes (e.g., sewage sludge) is suggested to improve economic viability but is not quantified.  
+No specific annual cost savings or revenue figures are directly reported in the contexts.</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -3570,7 +3595,7 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>The provided contexts do not explicitly report the total annual energy input (GJ/yr) for anaerobic digestion (AD) alone, AD integrated with an open pond system (OPS), or AD integrated with an algal turf scrubber (ATS). While energy consumption allocations and net energy outputs are discussed (e.g., AD being energetically favorable compared to other scenarios [2], and net energy outputs up to 854 GJ/yr for integrated systems [7]), specific values for total annual energy inputs are not quantified in the contexts provided.</t>
+          <t>The provided contexts do not explicitly report the total annual energy input (GJ/yr) for anaerobic digestion (AD) alone, AD integrated with an open pond system (OPS), or AD integrated with an algal turf scrubber (ATS). While energy consumption allocations and relative differences between systems are discussed (e.g., infrastructure burdens accounting for 50% of total energy use in OPS vs. 10% in ATS [5]), specific numerical values for total annual energy inputs are not quantified in the contexts.</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
@@ -3662,13 +3687,14 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>The organic loading rate (OLR) applied to the control reactor and microwave-pretreated reactor at a 15-day hydraulic retention time (HRT) was **0.99 g VS/L/day** (control) and **0.92 g VS/L/day** (pretreated), respectively. These values are reported in Table 2 of the study [7].</t>
+          <t>The organic loading rate (OLR) applied to the control reactor and microwave-pretreated reactor at a 15-day HRT was **0.99 g VS/L/day** (control) and **0.92 g VS/L/day** (pretreated), respectively. These values are reported in Table 2 of the study [7].</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>The organic loading rate (OLR) applied to both the control and microwave-pretreated reactors at a 15-day hydraulic retention time (HRT) was approximately **1.0 g VS/L/day**. This value was measured during the first experimental period when the reactors were operated at 15 days HRT [2]. 
-The OLR decreased to **0.75 g VS/L/day** during the subsequent period when the HRT was extended to 20 days [2]. No specific differences in OLR between the control and pretreated reactors were reported for the 15-day HRT condition, as both reactors were operated under identical HRT and feeding regimes during this period.</t>
+          <t>The organic loading rate (OLR) applied to both the control and microwave-pretreated reactors at a 15-day hydraulic retention time (HRT) was approximately **1.0 g VS/L/day**. This value was measured during the first experimental period when the reactors were operated at a 15-day HRT [2]. 
+The OLR decreased to **0.75 g VS/L/day** during the subsequent period when the HRT was extended to 20 days, but this applies to the second phase of the experiment and is not relevant to the 15-day HRT condition specifically asked in the question. 
+No distinction in OLR between the control and pretreated reactors is explicitly mentioned in the context, implying that the same OLR was applied to both under identical HRT conditions.</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -3743,12 +3769,12 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>The proximate analysis of **Cladophora rupestris** (Chlorophyta) reported a **water content of 74.1 ± 2.0%** and a **carbohydrate content of 39.9 ± 0.8%** (dry weight basis). These values are derived from Table 1 in context [1], which provides proximate and ultimate analysis data for various seaweed species. The reference for this data is **Olsson et al., (2020)**.</t>
+          <t>The proximate analysis of **Cladophora rupestris** (Chlorophyta) reported a **water content of 74.1 ± 2.0%** and a **carbohydrate content of 39.9 ± 0.8%** (dry weight basis). These values are sourced from Table 1 in context [1], with references to Olsson et al., (2020).</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>The provided contexts do not mention **Cladophora rupestris** or report specific water content or carbohydrate content values for this species. The proximate and ultimate analysis data referenced in the contexts pertain to other algae (e.g., *Ulva*, *Chlorella*, *Scenedesmus*) or seaweed species, but not *Cladophora rupestris*. Therefore, the answer cannot be determined from the given materials.</t>
+          <t>The provided contexts do not mention Cladophora rupestris or report specific water content or carbohydrate content values for this species. Therefore, the answer cannot be determined from the given information.</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -3824,14 +3850,10 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>For Sargassum sp. biochar produced by pyrolysis, the carbon (C) and nitrogen (N) contents at 400°C and 500°C are as follows:  
-- **At 400°C**:  
-  - Carbon (C): **51.28%**  
-  - Nitrogen (N): **1.38%**  
-- **At 500°C**:  
-  - Carbon (C): **52.58%**  
-  - Nitrogen (N): **1.32%**  
-These values are derived from Table 1 in context [6], which reports the chemical composition of biochar produced via pyrolysis under the specified conditions. The carbon content increases slightly with temperature, while the nitrogen content decreases marginally.</t>
+          <t>For Sargassum sp. biochar produced by pyrolysis:  
+- At **400°C**, the carbon (C) content was **51.28%** and nitrogen (N) content was **1.38%** [6].  
+- At **500°C**, the carbon content increased slightly to **52.58%**, while the nitrogen content decreased to **1.32%** [6].  
+These values are derived from Table 1 in context [6], which reports the elemental composition of biochar produced under different pyrolysis temperatures.</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -3916,16 +3938,13 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>For the landfill with landfill-gas recovery (LF_LFG) process in the environmental benefit grading framework:  
-- **Net energy benefit**: **423 kWh·t TS⁻¹** [1].  
-- **Net CO₂e emissions**: **0.83 t CO₂·t TS⁻¹** [1].  
-- **Total grade**: **1.94** (out of 9) [1].  
-These values are derived from Table 3 in context [1], which evaluates environmental benefits under different process scenarios.</t>
+          <t>In the environmental benefit grading framework, the landfill with landfill-gas recovery (LF_LFG) process reported a **net energy benefit of 423 kWh·t TS⁻¹** and **net CO₂e emissions of 0.83 t CO₂·t TS⁻¹**. The process received a **total grade of 1.94** (out of 9) [1]. 
+These values are derived from the "LF_LFGa" row in Table 3 of context [1], which corresponds to the specified process scenario.</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>The specific numerical values for the net energy benefit (kWh per t TS) and net CO2e emissions (t CO2 per t TS) for the landfill with landfill-gas recovery (LF_LFG) process, as well as its total grade in the environmental benefit grading framework, are **not explicitly reported** in the provided contexts. While the contexts discuss landfill gas recovery, energy balances, and CO2e emissions equations (e.g., Eq. 9 in [10] and Eq. 6 in [2]), they do not provide direct data for the LF_LFG process's net energy benefit or CO2e emissions. Additionally, the grading framework mentioned in [8] does not assign specific grades to LF_LFG. Therefore, the answer cannot be determined from the given information.</t>
+          <t>The provided contexts do not explicitly report the net energy benefit (kWh per t TS) or net CO₂e emissions (t CO₂ per t TS) for the landfill with landfill-gas recovery (LF_LFG) process, nor do they specify a total grade for this process in the environmental benefit grading framework. While some contexts discuss landfill gas (LFG) emissions, energy recovery, and grading criteria (e.g., residual waste quantities influencing grades [8]), specific numerical values for LF_LFG are absent. Therefore, the answer cannot be determined from the given contexts.</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -4005,19 +4024,16 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>For COD solubilization kinetics under thermal pretreatment (T70 condition), the fitted Korsmeyer–Peppas parameters and RMSE are as follows:  
+          <t>For the T70 condition (thermal pretreatment at 70°C), the fitted Korsmeyer–Peppas parameters and RMSE are as follows:  
 - **Kkp** = 35.38 min⁻ⁿ (95% CI: 33.9–36.9)  
 - **n** = 0.19 (95% CI: 0.17–0.21)  
 - **RMSE** = 3.09%  
-These values are derived from Table 5 in context [2], which provides kinetic parameters for different pretreatment conditions. The Korsmeyer–Peppas model was selected as the best fit for T70, with a high R² value of 0.99.</t>
+These values are derived from Table 5 in the study [2]. The model provided the best fit for this condition, with an R² of 0.99 and an AICc of 56.9 [2].</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>The Korsmeyer–Peppas parameters for the T70 condition (thermal pretreatment at $70^\circ \mathrm{C}$) are:  
-- **Kinetic constant** $K_{kp} = 35.38 \, \mathrm{min^{-n}}$  
-- **Diffusion exponent** $n = 0.19$  
-However, the **RMSE** (root mean square error) for this condition is **not explicitly reported** in the provided contexts. The text mentions that the Korsmeyer–Peppas model provided the best fit for each pretreatment condition but does not include numerical values for RMSE or other goodness-of-fit metrics for T70 [1].</t>
+          <t>The Korsmeyer–Peppas parameters for COD solubilization under thermal pretreatment at 70°C (T70) were reported as $ K_{kp} = 35.38 \, \text{min}^{-n} $ and $ n = 0.19 $. However, the context does not explicitly provide the RMSE (root mean square error) value for this condition [1].</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -4227,7 +4243,7 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.901</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="3">
@@ -4277,7 +4293,7 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.854</v>
+        <v>0.821</v>
       </c>
     </row>
     <row r="4">
@@ -4479,10 +4495,10 @@
         <v>0</v>
       </c>
       <c r="K8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>1</v>
@@ -4511,7 +4527,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
@@ -4538,7 +4554,7 @@
         <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="10">
@@ -4725,34 +4741,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -4775,7 +4791,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -4796,10 +4812,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0.889</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -5013,10 +5029,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.909</v>
+        <v>0.75</v>
       </c>
       <c r="N20" t="n">
-        <v>0.958</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="21">
@@ -5066,7 +5082,7 @@
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>0.998</v>
+        <v>0.977</v>
       </c>
     </row>
     <row r="22">
@@ -5259,13 +5275,13 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -5277,7 +5293,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -5324,7 +5340,7 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -5582,13 +5598,13 @@
         <v>0</v>
       </c>
       <c r="K33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -5796,10 +5812,13 @@
         <v>0</v>
       </c>
       <c r="K38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="b">
         <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.667</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -5846,7 +5865,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -6059,11 +6078,8 @@
       <c r="L44" t="b">
         <v>0</v>
       </c>
-      <c r="M44" t="n">
-        <v>1</v>
-      </c>
       <c r="N44" t="n">
-        <v>0.803</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="45">
@@ -6107,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.2</v>
+        <v>0.889</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -6324,7 +6340,7 @@
         <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>0.973</v>
+        <v>0.976</v>
       </c>
     </row>
     <row r="51">
@@ -6371,7 +6387,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
@@ -6899,7 +6915,7 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>0.429</v>
+        <v>0.571</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
@@ -7116,7 +7132,7 @@
         <v>1</v>
       </c>
       <c r="N68" t="n">
-        <v>0.787</v>
+        <v>0.8110000000000001</v>
       </c>
     </row>
     <row r="69">
@@ -7166,7 +7182,7 @@
         <v>1</v>
       </c>
       <c r="N69" t="n">
-        <v>0.726</v>
+        <v>0.781</v>
       </c>
     </row>
     <row r="70">
@@ -7377,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>0.787</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="75">
@@ -7634,6 +7650,9 @@
       <c r="L80" t="b">
         <v>0</v>
       </c>
+      <c r="M80" t="n">
+        <v>1</v>
+      </c>
       <c r="N80" t="n">
         <v>0.956</v>
       </c>
@@ -7682,7 +7701,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="N81" t="n">
         <v>0</v>
@@ -7899,7 +7918,7 @@
         <v>1</v>
       </c>
       <c r="N86" t="n">
-        <v>0.906</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="87">
@@ -7946,7 +7965,7 @@
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>0.857</v>
+        <v>0.571</v>
       </c>
       <c r="N87" t="n">
         <v>0</v>
@@ -8163,7 +8182,7 @@
         <v>1</v>
       </c>
       <c r="N92" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.871</v>
       </c>
     </row>
     <row r="93">
@@ -9073,16 +9092,16 @@
         <v>8</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>0.6343</v>
+        <v>0.6318</v>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>list</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>1-s2.0-S001623612201403X-main.pdf</t>
+          <t>technoeconomic_feasibility_macroalgae_ad.pdf</t>
         </is>
       </c>
       <c r="G19" s="13" t="b">
@@ -9090,7 +9109,7 @@
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>chunk-51130808d57dc234328ada6b41c32423</t>
+          <t>chunk-cc3a95194580208f42279b16448492d2</t>
         </is>
       </c>
     </row>
@@ -9109,16 +9128,16 @@
         <v>9</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>0.6318</v>
+        <v>0.6286</v>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>technoeconomic_feasibility_macroalgae_ad.pdf</t>
+          <t>biofuel_production_marine_macroalgae.pdf</t>
         </is>
       </c>
       <c r="G20" s="13" t="b">
@@ -9126,7 +9145,7 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>chunk-cc3a95194580208f42279b16448492d2</t>
+          <t>chunk-3757051f2d31070166ced5e36ac4e7b5</t>
         </is>
       </c>
     </row>
@@ -9145,7 +9164,7 @@
         <v>10</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.6286</v>
+        <v>0.6243</v>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
@@ -9154,7 +9173,7 @@
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>biofuel_production_marine_macroalgae.pdf</t>
+          <t>methane_yield_enhancement.pdf</t>
         </is>
       </c>
       <c r="G21" s="13" t="b">
@@ -9162,7 +9181,7 @@
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>chunk-3757051f2d31070166ced5e36ac4e7b5</t>
+          <t>chunk-18cf18a23ff73d8c31242febc26a0e64</t>
         </is>
       </c>
     </row>
@@ -9577,7 +9596,7 @@
         <v>2</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>0.6096</v>
+        <v>0.6045</v>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
@@ -9586,7 +9605,7 @@
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>1-s2.0-S001623612201403X-main.pdf</t>
+          <t>10.3390_pr12122794.pdf</t>
         </is>
       </c>
       <c r="G33" s="13" t="b">
@@ -9594,7 +9613,7 @@
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>chunk-d71cb5677387d261a22630aadcde5f65</t>
+          <t>chunk-dfa3b95d9c01b70f03de0222c09419f9</t>
         </is>
       </c>
     </row>
@@ -9613,7 +9632,7 @@
         <v>3</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>0.6045</v>
+        <v>0.6014</v>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
@@ -9630,7 +9649,7 @@
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>chunk-dfa3b95d9c01b70f03de0222c09419f9</t>
+          <t>chunk-455956b551378deb88480581cfc0b154</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9668,7 @@
         <v>4</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>0.6014</v>
+        <v>0.5974</v>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
@@ -9658,7 +9677,7 @@
       </c>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>10.3390_pr12122794.pdf</t>
+          <t>seasonal_variation_biogas_upgrading.pdf</t>
         </is>
       </c>
       <c r="G35" s="13" t="b">
@@ -9666,7 +9685,7 @@
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>chunk-455956b551378deb88480581cfc0b154</t>
+          <t>chunk-e3e54becf2edf6ba86907ed866692114</t>
         </is>
       </c>
     </row>
@@ -9685,7 +9704,7 @@
         <v>5</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>0.5997</v>
+        <v>0.5969</v>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
@@ -9694,7 +9713,7 @@
       </c>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>1-s2.0-S2211926425004011-main.pdf</t>
+          <t>microalgal_biotech_platform.pdf</t>
         </is>
       </c>
       <c r="G36" s="13" t="b">
@@ -9702,7 +9721,7 @@
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>chunk-1aaa6270638bdfaf20783104d9b3c80b</t>
+          <t>chunk-0251ac66da6eddb6ab4f3e0a95fd4452</t>
         </is>
       </c>
     </row>
@@ -9721,7 +9740,7 @@
         <v>6</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>0.5974</v>
+        <v>0.5888</v>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
@@ -9730,7 +9749,7 @@
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>seasonal_variation_biogas_upgrading.pdf</t>
+          <t>simultaneous_biogas_upgrading_centrate.pdf</t>
         </is>
       </c>
       <c r="G37" s="13" t="b">
@@ -9738,7 +9757,7 @@
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>chunk-e3e54becf2edf6ba86907ed866692114</t>
+          <t>chunk-a0924655cc95cad4232b6f368db0f3b2</t>
         </is>
       </c>
     </row>
@@ -9757,24 +9776,24 @@
         <v>7</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>0.5969</v>
+        <v>0.5814</v>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>list</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>microalgal_biotech_platform.pdf</t>
+          <t>insights_microalgaebased_technologies.pdf</t>
         </is>
       </c>
       <c r="G38" s="13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>chunk-0251ac66da6eddb6ab4f3e0a95fd4452</t>
+          <t>chunk-9169645702bb047aba23c9a0c7deec82</t>
         </is>
       </c>
     </row>
@@ -9793,7 +9812,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>0.5888</v>
+        <v>0.5784</v>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
@@ -9802,7 +9821,7 @@
       </c>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>simultaneous_biogas_upgrading_centrate.pdf</t>
+          <t>1-s2.0-S2211926417310366-main.pdf</t>
         </is>
       </c>
       <c r="G39" s="13" t="b">
@@ -9810,7 +9829,7 @@
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>chunk-a0924655cc95cad4232b6f368db0f3b2</t>
+          <t>chunk-d9c0b7b86b3df74891e0f2fc32944d32</t>
         </is>
       </c>
     </row>
@@ -9829,24 +9848,24 @@
         <v>9</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>0.5814</v>
+        <v>0.5743</v>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr">
         <is>
-          <t>insights_microalgaebased_technologies.pdf</t>
+          <t>10.3390_pr12122794.pdf</t>
         </is>
       </c>
       <c r="G40" s="13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>chunk-9169645702bb047aba23c9a0c7deec82</t>
+          <t>chunk-218530eb7b8a86528834ec18bad1fd8b</t>
         </is>
       </c>
     </row>
@@ -9865,7 +9884,7 @@
         <v>10</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>0.5784</v>
+        <v>0.5735</v>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
@@ -9882,7 +9901,7 @@
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>chunk-d9c0b7b86b3df74891e0f2fc32944d32</t>
+          <t>chunk-8dca174673b29a79d1bb77e8b007efdb</t>
         </is>
       </c>
     </row>
@@ -9901,7 +9920,7 @@
         <v>1</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>0.6435999999999999</v>
+        <v>0.6408</v>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
@@ -9910,15 +9929,15 @@
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>1-s2.0-S0960852425005577-main.pdf</t>
+          <t>insights_microalgaebased_technologies.pdf</t>
         </is>
       </c>
       <c r="G42" s="13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>chunk-07165584201fc31707b2089f8d1c4a47</t>
+          <t>chunk-24454d8f1ff9ac31783e73cd1304ca99</t>
         </is>
       </c>
     </row>
@@ -9937,24 +9956,24 @@
         <v>2</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>0.6408</v>
+        <v>0.636</v>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>image</t>
         </is>
       </c>
       <c r="F43" s="13" t="inlineStr">
         <is>
-          <t>insights_microalgaebased_technologies.pdf</t>
+          <t>comprehensive_review_biomethane_production.pdf</t>
         </is>
       </c>
       <c r="G43" s="13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>chunk-24454d8f1ff9ac31783e73cd1304ca99</t>
+          <t>chunk-aa2a93badc9a96a90d8b1bf494edbfca</t>
         </is>
       </c>
     </row>
@@ -9973,16 +9992,16 @@
         <v>3</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>0.636</v>
+        <v>0.6237</v>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>comprehensive_review_biomethane_production.pdf</t>
+          <t>seasonal_variation_biogas_upgrading.pdf</t>
         </is>
       </c>
       <c r="G44" s="13" t="b">
@@ -9990,7 +10009,7 @@
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>chunk-aa2a93badc9a96a90d8b1bf494edbfca</t>
+          <t>chunk-ba06d899cbdb4e4299c5cc903124ec2d</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10028,7 @@
         <v>4</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.6235000000000001</v>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
@@ -10018,7 +10037,7 @@
       </c>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>1-s2.0-S0960852425005577-main.pdf</t>
+          <t>10.3390_pr12122794.pdf</t>
         </is>
       </c>
       <c r="G45" s="13" t="b">
@@ -10026,7 +10045,7 @@
       </c>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>chunk-bbb2d184af6cfff9503c7661f9236ab7</t>
+          <t>doc-88279f31e7b8e4ed6037d02a7cfaf18f-chunk-006</t>
         </is>
       </c>
     </row>
@@ -10045,7 +10064,7 @@
         <v>5</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>0.6237</v>
+        <v>0.6227</v>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
@@ -10054,15 +10073,15 @@
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>seasonal_variation_biogas_upgrading.pdf</t>
+          <t>insights_microalgaebased_technologies.pdf</t>
         </is>
       </c>
       <c r="G46" s="13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>chunk-ba06d899cbdb4e4299c5cc903124ec2d</t>
+          <t>chunk-08277ad4b2a1cbba7cdb54fcb1763fdf</t>
         </is>
       </c>
     </row>
@@ -10081,7 +10100,7 @@
         <v>6</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
@@ -10090,7 +10109,7 @@
       </c>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>10.3390_pr12122794.pdf</t>
+          <t>simultaneous_biogas_upgrading_centrate.pdf</t>
         </is>
       </c>
       <c r="G47" s="13" t="b">
@@ -10098,7 +10117,7 @@
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>doc-88279f31e7b8e4ed6037d02a7cfaf18f-chunk-006</t>
+          <t>chunk-ef01aeafc08e202d8234136cef719e84</t>
         </is>
       </c>
     </row>
@@ -10117,7 +10136,7 @@
         <v>7</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>0.6227</v>
+        <v>0.6185</v>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
@@ -10126,15 +10145,15 @@
       </c>
       <c r="F48" s="13" t="inlineStr">
         <is>
-          <t>insights_microalgaebased_technologies.pdf</t>
+          <t>microalgal_biotech_platform.pdf</t>
         </is>
       </c>
       <c r="G48" s="13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>chunk-08277ad4b2a1cbba7cdb54fcb1763fdf</t>
+          <t>chunk-0251ac66da6eddb6ab4f3e0a95fd4452</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10172,7 @@
         <v>8</v>
       </c>
       <c r="D49" s="13" t="n">
-        <v>0.6222</v>
+        <v>0.6177</v>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
@@ -10162,15 +10181,15 @@
       </c>
       <c r="F49" s="13" t="inlineStr">
         <is>
-          <t>1-s2.0-S0960852425005577-main.pdf</t>
+          <t>insights_microalgaebased_technologies.pdf</t>
         </is>
       </c>
       <c r="G49" s="13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>chunk-e76744c55690b1d49034ba5af69ee9f3</t>
+          <t>chunk-58c70a2d9d50354a4a0b0870f0b42f69</t>
         </is>
       </c>
     </row>
@@ -10189,16 +10208,16 @@
         <v>9</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.6175</v>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>image</t>
         </is>
       </c>
       <c r="F50" s="13" t="inlineStr">
         <is>
-          <t>simultaneous_biogas_upgrading_centrate.pdf</t>
+          <t>1-s2.0-S0960852423013834-main.pdf</t>
         </is>
       </c>
       <c r="G50" s="13" t="b">
@@ -10206,7 +10225,7 @@
       </c>
       <c r="H50" s="12" t="inlineStr">
         <is>
-          <t>chunk-ef01aeafc08e202d8234136cef719e84</t>
+          <t>chunk-c574451dadb3d1c7a3bfa5f08e56bd0b</t>
         </is>
       </c>
     </row>
@@ -10225,7 +10244,7 @@
         <v>10</v>
       </c>
       <c r="D51" s="13" t="n">
-        <v>0.6185</v>
+        <v>0.6171</v>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
@@ -10234,7 +10253,7 @@
       </c>
       <c r="F51" s="13" t="inlineStr">
         <is>
-          <t>microalgal_biotech_platform.pdf</t>
+          <t>1-s2.0-S0960852423013834-main.pdf</t>
         </is>
       </c>
       <c r="G51" s="13" t="b">
@@ -10242,7 +10261,7 @@
       </c>
       <c r="H51" s="12" t="inlineStr">
         <is>
-          <t>chunk-0251ac66da6eddb6ab4f3e0a95fd4452</t>
+          <t>chunk-5375e6cb70e64050c721ba85c04495dd</t>
         </is>
       </c>
     </row>
@@ -10261,7 +10280,7 @@
         <v>1</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>0.6435999999999999</v>
+        <v>0.6408</v>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
@@ -10270,15 +10289,15 @@
       </c>
       <c r="F52" s="13" t="inlineStr">
         <is>
-          <t>1-s2.0-S0960852425005577-main.pdf</t>
+          <t>insights_microalgaebased_technologies.pdf</t>
         </is>
       </c>
       <c r="G52" s="13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>chunk-07165584201fc31707b2089f8d1c4a47</t>
+          <t>chunk-24454d8f1ff9ac31783e73cd1304ca99</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10316,7 @@
         <v>2</v>
       </c>
       <c r="D53" s="13" t="n">
-        <v>0.6408</v>
+        <v>0.6237</v>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
@@ -10306,15 +10325,15 @@
       </c>
       <c r="F53" s="13" t="inlineStr">
         <is>
-          <t>insights_microalgaebased_technologies.pdf</t>
+          <t>seasonal_variation_biogas_upgrading.pdf</t>
         </is>
       </c>
       <c r="G53" s="13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" s="12" t="inlineStr">
         <is>
-          <t>chunk-24454d8f1ff9ac31783e73cd1304ca99</t>
+          <t>chunk-ba06d899cbdb4e4299c5cc903124ec2d</t>
         </is>
       </c>
     </row>
@@ -10333,7 +10352,7 @@
         <v>3</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.6235000000000001</v>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
@@ -10342,7 +10361,7 @@
       </c>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>1-s2.0-S0960852425005577-main.pdf</t>
+          <t>10.3390_pr12122794.pdf</t>
         </is>
       </c>
       <c r="G54" s="13" t="b">
@@ -10350,7 +10369,7 @@
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
-          <t>chunk-bbb2d184af6cfff9503c7661f9236ab7</t>
+          <t>doc-88279f31e7b8e4ed6037d02a7cfaf18f-chunk-006</t>
         </is>
       </c>
     </row>
@@ -10369,7 +10388,7 @@
         <v>4</v>
       </c>
       <c r="D55" s="13" t="n">
-        <v>0.6237</v>
+        <v>0.6227</v>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
@@ -10378,15 +10397,15 @@
       </c>
       <c r="F55" s="13" t="inlineStr">
         <is>
-          <t>seasonal_variation_biogas_upgrading.pdf</t>
+          <t>insights_microalgaebased_technologies.pdf</t>
         </is>
       </c>
       <c r="G55" s="13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" s="12" t="inlineStr">
         <is>
-          <t>chunk-ba06d899cbdb4e4299c5cc903124ec2d</t>
+          <t>chunk-08277ad4b2a1cbba7cdb54fcb1763fdf</t>
         </is>
       </c>
     </row>
@@ -10405,7 +10424,7 @@
         <v>5</v>
       </c>
       <c r="D56" s="13" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
@@ -10414,7 +10433,7 @@
       </c>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>10.3390_pr12122794.pdf</t>
+          <t>simultaneous_biogas_upgrading_centrate.pdf</t>
         </is>
       </c>
       <c r="G56" s="13" t="b">
@@ -10422,7 +10441,7 @@
       </c>
       <c r="H56" s="12" t="inlineStr">
         <is>
-          <t>doc-88279f31e7b8e4ed6037d02a7cfaf18f-chunk-006</t>
+          <t>chunk-ef01aeafc08e202d8234136cef719e84</t>
         </is>
       </c>
     </row>
@@ -10441,7 +10460,7 @@
         <v>6</v>
       </c>
       <c r="D57" s="13" t="n">
-        <v>0.6227</v>
+        <v>0.6185</v>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
@@ -10450,15 +10469,15 @@
       </c>
       <c r="F57" s="13" t="inlineStr">
         <is>
-          <t>insights_microalgaebased_technologies.pdf</t>
+          <t>microalgal_biotech_platform.pdf</t>
         </is>
       </c>
       <c r="G57" s="13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" s="12" t="inlineStr">
         <is>
-          <t>chunk-08277ad4b2a1cbba7cdb54fcb1763fdf</t>
+          <t>chunk-0251ac66da6eddb6ab4f3e0a95fd4452</t>
         </is>
       </c>
     </row>
@@ -10477,7 +10496,7 @@
         <v>7</v>
       </c>
       <c r="D58" s="13" t="n">
-        <v>0.6222</v>
+        <v>0.6177</v>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
@@ -10486,15 +10505,15 @@
       </c>
       <c r="F58" s="13" t="inlineStr">
         <is>
-          <t>1-s2.0-S0960852425005577-main.pdf</t>
+          <t>insights_microalgaebased_technologies.pdf</t>
         </is>
       </c>
       <c r="G58" s="13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" s="12" t="inlineStr">
         <is>
-          <t>chunk-e76744c55690b1d49034ba5af69ee9f3</t>
+          <t>chunk-58c70a2d9d50354a4a0b0870f0b42f69</t>
         </is>
       </c>
     </row>
@@ -10513,7 +10532,7 @@
         <v>8</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.6171</v>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
@@ -10522,7 +10541,7 @@
       </c>
       <c r="F59" s="13" t="inlineStr">
         <is>
-          <t>simultaneous_biogas_upgrading_centrate.pdf</t>
+          <t>1-s2.0-S0960852423013834-main.pdf</t>
         </is>
       </c>
       <c r="G59" s="13" t="b">
@@ -10530,7 +10549,7 @@
       </c>
       <c r="H59" s="12" t="inlineStr">
         <is>
-          <t>chunk-ef01aeafc08e202d8234136cef719e84</t>
+          <t>chunk-5375e6cb70e64050c721ba85c04495dd</t>
         </is>
       </c>
     </row>
@@ -10549,7 +10568,7 @@
         <v>9</v>
       </c>
       <c r="D60" s="13" t="n">
-        <v>0.6185</v>
+        <v>0.6167</v>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
@@ -10566,7 +10585,7 @@
       </c>
       <c r="H60" s="12" t="inlineStr">
         <is>
-          <t>chunk-0251ac66da6eddb6ab4f3e0a95fd4452</t>
+          <t>chunk-efd9413008fe90740c86dbab0a0c16ff</t>
         </is>
       </c>
     </row>
@@ -10585,7 +10604,7 @@
         <v>10</v>
       </c>
       <c r="D61" s="13" t="n">
-        <v>0.6177</v>
+        <v>0.6165</v>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
@@ -10594,15 +10613,15 @@
       </c>
       <c r="F61" s="13" t="inlineStr">
         <is>
-          <t>insights_microalgaebased_technologies.pdf</t>
+          <t>microalgal_biotech_platform.pdf</t>
         </is>
       </c>
       <c r="G61" s="13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" s="12" t="inlineStr">
         <is>
-          <t>chunk-58c70a2d9d50354a4a0b0870f0b42f69</t>
+          <t>chunk-aabd8cd0004138bd3b6e5e7a0ff8086e</t>
         </is>
       </c>
     </row>
@@ -12853,16 +12872,16 @@
         <v>3</v>
       </c>
       <c r="D124" s="13" t="n">
-        <v>0.6178</v>
+        <v>0.6148</v>
       </c>
       <c r="E124" s="13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>table</t>
         </is>
       </c>
       <c r="F124" s="13" t="inlineStr">
         <is>
-          <t>1-s2.0-S0360319925051365-main.pdf</t>
+          <t>10.1016_j.biortech.2024.130381.pdf</t>
         </is>
       </c>
       <c r="G124" s="13" t="b">
@@ -12870,7 +12889,7 @@
       </c>
       <c r="H124" s="12" t="inlineStr">
         <is>
-          <t>chunk-1deba058b2bac847c02d911acff3a32b</t>
+          <t>chunk-f274824c825b0d6ca4ffb0238d9e4c7f</t>
         </is>
       </c>
     </row>
@@ -12889,7 +12908,7 @@
         <v>4</v>
       </c>
       <c r="D125" s="13" t="n">
-        <v>0.6148</v>
+        <v>0.6086</v>
       </c>
       <c r="E125" s="13" t="inlineStr">
         <is>
@@ -12898,15 +12917,15 @@
       </c>
       <c r="F125" s="13" t="inlineStr">
         <is>
-          <t>10.1016_j.biortech.2024.130381.pdf</t>
+          <t>10.1016_j.compchemeng.2025.109409.pdf</t>
         </is>
       </c>
       <c r="G125" s="13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H125" s="12" t="inlineStr">
         <is>
-          <t>chunk-f274824c825b0d6ca4ffb0238d9e4c7f</t>
+          <t>chunk-7ba78052ff9ba7589c7e9cd0e6721f88</t>
         </is>
       </c>
     </row>
@@ -12925,7 +12944,7 @@
         <v>5</v>
       </c>
       <c r="D126" s="13" t="n">
-        <v>0.6086</v>
+        <v>0.5986</v>
       </c>
       <c r="E126" s="13" t="inlineStr">
         <is>
@@ -12934,15 +12953,15 @@
       </c>
       <c r="F126" s="13" t="inlineStr">
         <is>
-          <t>10.1016_j.compchemeng.2025.109409.pdf</t>
+          <t>waste_valorization_strategies_inputs.pdf</t>
         </is>
       </c>
       <c r="G126" s="13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H126" s="12" t="inlineStr">
         <is>
-          <t>chunk-7ba78052ff9ba7589c7e9cd0e6721f88</t>
+          <t>chunk-31f3ffb00a6991889f8d59247fe0b509</t>
         </is>
       </c>
     </row>
@@ -12961,16 +12980,16 @@
         <v>6</v>
       </c>
       <c r="D127" s="13" t="n">
-        <v>0.5986</v>
+        <v>0.5984</v>
       </c>
       <c r="E127" s="13" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F127" s="13" t="inlineStr">
         <is>
-          <t>waste_valorization_strategies_inputs.pdf</t>
+          <t>10.1016_j.cosust.2026.101605.pdf</t>
         </is>
       </c>
       <c r="G127" s="13" t="b">
@@ -12978,7 +12997,7 @@
       </c>
       <c r="H127" s="12" t="inlineStr">
         <is>
-          <t>chunk-31f3ffb00a6991889f8d59247fe0b509</t>
+          <t>doc-6a55f8abf8a48c5d1d888c2553ade166-chunk-003</t>
         </is>
       </c>
     </row>
@@ -12997,7 +13016,7 @@
         <v>7</v>
       </c>
       <c r="D128" s="13" t="n">
-        <v>0.5984</v>
+        <v>0.5956</v>
       </c>
       <c r="E128" s="13" t="inlineStr">
         <is>
@@ -13006,7 +13025,7 @@
       </c>
       <c r="F128" s="13" t="inlineStr">
         <is>
-          <t>10.1016_j.cosust.2026.101605.pdf</t>
+          <t>breaking_barriers_largescale_microalgae.pdf</t>
         </is>
       </c>
       <c r="G128" s="13" t="b">
@@ -13014,7 +13033,7 @@
       </c>
       <c r="H128" s="12" t="inlineStr">
         <is>
-          <t>doc-6a55f8abf8a48c5d1d888c2553ade166-chunk-003</t>
+          <t>chunk-a862010653250ea23965c36bdacd45e6</t>
         </is>
       </c>
     </row>
@@ -13033,16 +13052,16 @@
         <v>8</v>
       </c>
       <c r="D129" s="13" t="n">
-        <v>0.5956</v>
+        <v>0.5951</v>
       </c>
       <c r="E129" s="13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>table</t>
         </is>
       </c>
       <c r="F129" s="13" t="inlineStr">
         <is>
-          <t>breaking_barriers_largescale_microalgae.pdf</t>
+          <t>critical_review_microalgae_cyanobacteria.pdf</t>
         </is>
       </c>
       <c r="G129" s="13" t="b">
@@ -13050,7 +13069,7 @@
       </c>
       <c r="H129" s="12" t="inlineStr">
         <is>
-          <t>chunk-a862010653250ea23965c36bdacd45e6</t>
+          <t>chunk-9a9097173f352380a69eefd7388e16ef</t>
         </is>
       </c>
     </row>
@@ -13069,7 +13088,7 @@
         <v>9</v>
       </c>
       <c r="D130" s="13" t="n">
-        <v>0.5951</v>
+        <v>0.5942</v>
       </c>
       <c r="E130" s="13" t="inlineStr">
         <is>
@@ -13078,7 +13097,7 @@
       </c>
       <c r="F130" s="13" t="inlineStr">
         <is>
-          <t>critical_review_microalgae_cyanobacteria.pdf</t>
+          <t>recent_advances_microalgae_cultivation.pdf</t>
         </is>
       </c>
       <c r="G130" s="13" t="b">
@@ -13086,7 +13105,7 @@
       </c>
       <c r="H130" s="12" t="inlineStr">
         <is>
-          <t>chunk-9a9097173f352380a69eefd7388e16ef</t>
+          <t>chunk-2abb135c023293c362e20f85290917e4</t>
         </is>
       </c>
     </row>
@@ -13105,24 +13124,24 @@
         <v>10</v>
       </c>
       <c r="D131" s="13" t="n">
-        <v>0.5942</v>
+        <v>0.5937</v>
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F131" s="13" t="inlineStr">
         <is>
-          <t>recent_advances_microalgae_cultivation.pdf</t>
+          <t>10.1016_j.compchemeng.2025.109409.pdf</t>
         </is>
       </c>
       <c r="G131" s="13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H131" s="12" t="inlineStr">
         <is>
-          <t>chunk-2abb135c023293c362e20f85290917e4</t>
+          <t>chunk-58b71d4b0e839877ec45fb053b0436ee</t>
         </is>
       </c>
     </row>
@@ -13141,7 +13160,7 @@
         <v>1</v>
       </c>
       <c r="D132" s="13" t="n">
-        <v>0.6178</v>
+        <v>0.5984</v>
       </c>
       <c r="E132" s="13" t="inlineStr">
         <is>
@@ -13150,7 +13169,7 @@
       </c>
       <c r="F132" s="13" t="inlineStr">
         <is>
-          <t>1-s2.0-S0360319925051365-main.pdf</t>
+          <t>10.1016_j.cosust.2026.101605.pdf</t>
         </is>
       </c>
       <c r="G132" s="13" t="b">
@@ -13158,7 +13177,7 @@
       </c>
       <c r="H132" s="12" t="inlineStr">
         <is>
-          <t>chunk-1deba058b2bac847c02d911acff3a32b</t>
+          <t>doc-6a55f8abf8a48c5d1d888c2553ade166-chunk-003</t>
         </is>
       </c>
     </row>
@@ -13177,7 +13196,7 @@
         <v>2</v>
       </c>
       <c r="D133" s="13" t="n">
-        <v>0.5984</v>
+        <v>0.5956</v>
       </c>
       <c r="E133" s="13" t="inlineStr">
         <is>
@@ -13186,7 +13205,7 @@
       </c>
       <c r="F133" s="13" t="inlineStr">
         <is>
-          <t>10.1016_j.cosust.2026.101605.pdf</t>
+          <t>breaking_barriers_largescale_microalgae.pdf</t>
         </is>
       </c>
       <c r="G133" s="13" t="b">
@@ -13194,7 +13213,7 @@
       </c>
       <c r="H133" s="12" t="inlineStr">
         <is>
-          <t>doc-6a55f8abf8a48c5d1d888c2553ade166-chunk-003</t>
+          <t>chunk-a862010653250ea23965c36bdacd45e6</t>
         </is>
       </c>
     </row>
@@ -13213,7 +13232,7 @@
         <v>3</v>
       </c>
       <c r="D134" s="13" t="n">
-        <v>0.5956</v>
+        <v>0.5936</v>
       </c>
       <c r="E134" s="13" t="inlineStr">
         <is>
@@ -13222,7 +13241,7 @@
       </c>
       <c r="F134" s="13" t="inlineStr">
         <is>
-          <t>breaking_barriers_largescale_microalgae.pdf</t>
+          <t>integrating_microalgae_growth_biomethane.pdf</t>
         </is>
       </c>
       <c r="G134" s="13" t="b">
@@ -13230,7 +13249,7 @@
       </c>
       <c r="H134" s="12" t="inlineStr">
         <is>
-          <t>chunk-a862010653250ea23965c36bdacd45e6</t>
+          <t>chunk-39e52a5155655fd15148308e53fd9131</t>
         </is>
       </c>
     </row>
@@ -13249,7 +13268,7 @@
         <v>4</v>
       </c>
       <c r="D135" s="13" t="n">
-        <v>0.5936</v>
+        <v>0.5906</v>
       </c>
       <c r="E135" s="13" t="inlineStr">
         <is>
@@ -13258,7 +13277,7 @@
       </c>
       <c r="F135" s="13" t="inlineStr">
         <is>
-          <t>integrating_microalgae_growth_biomethane.pdf</t>
+          <t>algae_biofuels_catalytic.pdf</t>
         </is>
       </c>
       <c r="G135" s="13" t="b">
@@ -13266,7 +13285,7 @@
       </c>
       <c r="H135" s="12" t="inlineStr">
         <is>
-          <t>chunk-39e52a5155655fd15148308e53fd9131</t>
+          <t>chunk-6fe8df477d6437123f6570d46a0854ac</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13304,7 @@
         <v>5</v>
       </c>
       <c r="D136" s="13" t="n">
-        <v>0.5906</v>
+        <v>0.5865</v>
       </c>
       <c r="E136" s="13" t="inlineStr">
         <is>
@@ -13302,7 +13321,7 @@
       </c>
       <c r="H136" s="12" t="inlineStr">
         <is>
-          <t>chunk-6fe8df477d6437123f6570d46a0854ac</t>
+          <t>chunk-4c6b7447b5965fbc8587c22adfaca880</t>
         </is>
       </c>
     </row>
@@ -13321,7 +13340,7 @@
         <v>6</v>
       </c>
       <c r="D137" s="13" t="n">
-        <v>0.5865</v>
+        <v>0.5858</v>
       </c>
       <c r="E137" s="13" t="inlineStr">
         <is>
@@ -13330,7 +13349,7 @@
       </c>
       <c r="F137" s="13" t="inlineStr">
         <is>
-          <t>algae_biofuels_catalytic.pdf</t>
+          <t>hard_reality_biogas.pdf</t>
         </is>
       </c>
       <c r="G137" s="13" t="b">
@@ -13338,7 +13357,7 @@
       </c>
       <c r="H137" s="12" t="inlineStr">
         <is>
-          <t>chunk-4c6b7447b5965fbc8587c22adfaca880</t>
+          <t>chunk-52682d5dfd4a9fff943314a7488c23d2</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13376,7 @@
         <v>7</v>
       </c>
       <c r="D138" s="13" t="n">
-        <v>0.5858</v>
+        <v>0.5849</v>
       </c>
       <c r="E138" s="13" t="inlineStr">
         <is>
@@ -13366,7 +13385,7 @@
       </c>
       <c r="F138" s="13" t="inlineStr">
         <is>
-          <t>hard_reality_biogas.pdf</t>
+          <t>10.1016_j.biortech.2016.03.102.pdf</t>
         </is>
       </c>
       <c r="G138" s="13" t="b">
@@ -13374,7 +13393,7 @@
       </c>
       <c r="H138" s="12" t="inlineStr">
         <is>
-          <t>chunk-52682d5dfd4a9fff943314a7488c23d2</t>
+          <t>doc-80c1a562237bdb88ff956104201017b5-chunk-006</t>
         </is>
       </c>
     </row>
@@ -13393,7 +13412,7 @@
         <v>8</v>
       </c>
       <c r="D139" s="13" t="n">
-        <v>0.5849</v>
+        <v>0.5846</v>
       </c>
       <c r="E139" s="13" t="inlineStr">
         <is>
@@ -13402,7 +13421,7 @@
       </c>
       <c r="F139" s="13" t="inlineStr">
         <is>
-          <t>10.1016_j.biortech.2016.03.102.pdf</t>
+          <t>critical_review_microalgae_cyanobacteria.pdf</t>
         </is>
       </c>
       <c r="G139" s="13" t="b">
@@ -13410,7 +13429,7 @@
       </c>
       <c r="H139" s="12" t="inlineStr">
         <is>
-          <t>doc-80c1a562237bdb88ff956104201017b5-chunk-006</t>
+          <t>chunk-0244e5aacdb0929be50993b5dfe1e37a</t>
         </is>
       </c>
     </row>
@@ -13429,7 +13448,7 @@
         <v>9</v>
       </c>
       <c r="D140" s="13" t="n">
-        <v>0.5846</v>
+        <v>0.583</v>
       </c>
       <c r="E140" s="13" t="inlineStr">
         <is>
@@ -13438,7 +13457,7 @@
       </c>
       <c r="F140" s="13" t="inlineStr">
         <is>
-          <t>critical_review_microalgae_cyanobacteria.pdf</t>
+          <t>1-s2.0-S0048969720356977-main.pdf</t>
         </is>
       </c>
       <c r="G140" s="13" t="b">
@@ -13446,7 +13465,7 @@
       </c>
       <c r="H140" s="12" t="inlineStr">
         <is>
-          <t>chunk-0244e5aacdb0929be50993b5dfe1e37a</t>
+          <t>chunk-1c0a21cf251626a2daa597d9e314f6ea</t>
         </is>
       </c>
     </row>
@@ -13465,7 +13484,7 @@
         <v>10</v>
       </c>
       <c r="D141" s="13" t="n">
-        <v>0.583</v>
+        <v>0.5824</v>
       </c>
       <c r="E141" s="13" t="inlineStr">
         <is>
@@ -13474,7 +13493,7 @@
       </c>
       <c r="F141" s="13" t="inlineStr">
         <is>
-          <t>1-s2.0-S0048969720356977-main.pdf</t>
+          <t>breaking_barriers_largescale_microalgae.pdf</t>
         </is>
       </c>
       <c r="G141" s="13" t="b">
@@ -13482,7 +13501,7 @@
       </c>
       <c r="H141" s="12" t="inlineStr">
         <is>
-          <t>chunk-1c0a21cf251626a2daa597d9e314f6ea</t>
+          <t>chunk-b7decf0877dadb838c711533ecc7c8b7</t>
         </is>
       </c>
     </row>
@@ -13757,7 +13776,7 @@
       </c>
       <c r="E149" s="13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>table</t>
         </is>
       </c>
       <c r="F149" s="13" t="inlineStr">
@@ -13770,7 +13789,7 @@
       </c>
       <c r="H149" s="12" t="inlineStr">
         <is>
-          <t>chunk-a77ed8c05151252d8d3ed17a15dac482</t>
+          <t>chunk-5c6b45edcf12e1cc5a086b15dd3e6009</t>
         </is>
       </c>
     </row>
@@ -13793,7 +13812,7 @@
       </c>
       <c r="E150" s="13" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F150" s="13" t="inlineStr">
@@ -13806,7 +13825,7 @@
       </c>
       <c r="H150" s="12" t="inlineStr">
         <is>
-          <t>chunk-5c6b45edcf12e1cc5a086b15dd3e6009</t>
+          <t>chunk-a77ed8c05151252d8d3ed17a15dac482</t>
         </is>
       </c>
     </row>
@@ -17785,7 +17804,7 @@
         <v>10</v>
       </c>
       <c r="D261" s="13" t="n">
-        <v>0.5256</v>
+        <v>0.5241</v>
       </c>
       <c r="E261" s="13" t="inlineStr">
         <is>
@@ -17794,7 +17813,7 @@
       </c>
       <c r="F261" s="13" t="inlineStr">
         <is>
-          <t>1-s2.0-S2211926425004011-main.pdf</t>
+          <t>hydrothermal_carbonization_microalgae_biomass.pdf</t>
         </is>
       </c>
       <c r="G261" s="13" t="b">
@@ -17802,7 +17821,7 @@
       </c>
       <c r="H261" s="12" t="inlineStr">
         <is>
-          <t>chunk-736eedcfdd49018705042a3aa334959d</t>
+          <t>chunk-e9bc3dc80232610b04a5e195758caa34</t>
         </is>
       </c>
     </row>
